--- a/result_table_templates/Ramp_analysis.xlsx
+++ b/result_table_templates/Ramp_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/letrungtran/Documents/MATLAB/DJ_schwartzlab/result_table_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{681EBB95-15F1-6E42-90F5-564C1227BA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1C7CCB-985C-5D41-8C18-F1663DE4043C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7940" yWindow="3960" windowWidth="26840" windowHeight="15680" xr2:uid="{75A91211-F42E-EA48-AA43-606FDB958255}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>Field</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>n_trial</t>
-  </si>
-  <si>
-    <t>uint8</t>
   </si>
   <si>
     <t xml:space="preserve">number of trials </t>
@@ -680,76 +677,76 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
         <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
